--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:44</t>
+    <t xml:space="preserve">2026-09-09 19:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:10</t>
+    <t xml:space="preserve">2026-09-17 04:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:25</t>
+    <t xml:space="preserve">2026-09-25 11:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 11:19</t>
+    <t xml:space="preserve">2026-09-26 23:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_metropolitana_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_metropolitana_provincial.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-26 23:52</t>
+    <t xml:space="preserve">2026-10-05 05:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
